--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Downloads/MaHIS dataset reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527C696A-FD28-A54D-B556-B9F30B5716C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B015B476-96E2-EC40-88B4-507110D1B955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18960" yWindow="760" windowWidth="15600" windowHeight="19400" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIABLE_NAMES" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="143">
   <si>
     <t>name</t>
   </si>
@@ -387,9 +387,6 @@
     <t>unique_column</t>
   </si>
   <si>
-    <t>encounter_id</t>
-  </si>
-  <si>
     <t>ValueN</t>
   </si>
   <si>
@@ -456,9 +453,6 @@
     <t>Counts</t>
   </si>
   <si>
-    <t>REGISTRATION</t>
-  </si>
-  <si>
     <t>MALARIA HEALTH FACILITY MONTHLY REPORT</t>
   </si>
   <si>
@@ -469,6 +463,12 @@
   </si>
   <si>
     <t>Patient pregnant | Primary diagnosis | Secondary diagnosis</t>
+  </si>
+  <si>
+    <t>person_id</t>
+  </si>
+  <si>
+    <t>programs</t>
   </si>
 </sst>
 </file>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" t="s">
         <v>133</v>
-      </c>
-      <c r="B2" t="s">
-        <v>134</v>
       </c>
       <c r="C2" t="s">
         <v>41</v>
@@ -1062,18 +1062,18 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" t="s">
         <v>136</v>
-      </c>
-      <c r="B19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D19" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
         <v>81</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
         <v>82</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
         <v>83</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
         <v>84</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
         <v>85</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
         <v>86</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
         <v>87</v>
@@ -1265,13 +1265,13 @@
         <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F2" t="s">
         <v>33</v>
@@ -1300,13 +1300,13 @@
         <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s">
         <v>33</v>
@@ -1335,13 +1335,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -1370,13 +1370,13 @@
         <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
@@ -1402,28 +1402,28 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F6" t="s">
         <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
@@ -1431,28 +1431,28 @@
         <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F7" t="s">
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H7" t="s">
         <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -1463,19 +1463,13 @@
         <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
@@ -1492,19 +1486,13 @@
         <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -1521,13 +1509,13 @@
         <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
@@ -1545,7 +1533,7 @@
         <v>99</v>
       </c>
       <c r="K10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
@@ -1556,13 +1544,13 @@
         <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -1580,7 +1568,7 @@
         <v>99</v>
       </c>
       <c r="K11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
@@ -1591,13 +1579,13 @@
         <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F12" t="s">
         <v>33</v>
@@ -1615,7 +1603,7 @@
         <v>99</v>
       </c>
       <c r="K12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
@@ -1626,13 +1614,13 @@
         <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F13" t="s">
         <v>33</v>
@@ -1650,10 +1638,10 @@
         <v>99</v>
       </c>
       <c r="K13" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -1661,13 +1649,13 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F14" t="s">
         <v>33</v>
@@ -1696,13 +1684,13 @@
         <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F15" t="s">
         <v>33</v>
@@ -1731,13 +1719,13 @@
         <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F16" t="s">
         <v>33</v>
@@ -1772,13 +1760,13 @@
         <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
         <v>33</v>
@@ -1813,13 +1801,13 @@
         <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
@@ -1831,7 +1819,7 @@
         <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J18" t="s">
         <v>39</v>
@@ -1848,13 +1836,13 @@
         <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F19" t="s">
         <v>33</v>
@@ -1866,7 +1854,7 @@
         <v>35</v>
       </c>
       <c r="I19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J19" t="s">
         <v>39</v>
@@ -1883,13 +1871,13 @@
         <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F20" t="s">
         <v>33</v>
@@ -1901,7 +1889,7 @@
         <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J20" t="s">
         <v>102</v>
@@ -1924,13 +1912,13 @@
         <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F21" t="s">
         <v>33</v>
@@ -1942,7 +1930,7 @@
         <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J21" t="s">
         <v>102</v>
@@ -1965,13 +1953,13 @@
         <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
         <v>33</v>
@@ -1994,13 +1982,13 @@
         <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F23" t="s">
         <v>33</v>
@@ -2023,13 +2011,13 @@
         <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F24" t="s">
         <v>33</v>
@@ -2052,13 +2040,13 @@
         <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
         <v>33</v>
@@ -2081,13 +2069,13 @@
         <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
         <v>33</v>
@@ -2110,13 +2098,13 @@
         <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
@@ -2145,13 +2133,13 @@
         <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
@@ -2174,13 +2162,13 @@
         <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F29" t="s">
         <v>33</v>
@@ -2203,13 +2191,13 @@
         <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F30" t="s">
         <v>33</v>
@@ -2232,13 +2220,13 @@
         <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
@@ -2261,13 +2249,13 @@
         <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
@@ -2290,13 +2278,13 @@
         <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
@@ -2323,26 +2311,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E53CD3-50A0-1347-AEEF-73E1C95C94BD}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>42</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>137</v>
+      </c>
+      <c r="C2" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2395,7 +2389,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>

--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Downloads/MaHIS dataset reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B015B476-96E2-EC40-88B4-507110D1B955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA81F7E-05B3-574D-86C2-703F2F2659FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="144">
   <si>
     <t>name</t>
   </si>
@@ -153,9 +153,6 @@
     <t>obs_value_coded</t>
   </si>
   <si>
-    <t>Malaria</t>
-  </si>
-  <si>
     <t>malaria_confirmed_over5</t>
   </si>
   <si>
@@ -469,6 +466,12 @@
   </si>
   <si>
     <t>programs</t>
+  </si>
+  <si>
+    <t>obs_value_coded | Value</t>
+  </si>
+  <si>
+    <t>Malaria | Positive</t>
   </si>
 </sst>
 </file>
@@ -843,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -878,16 +881,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
         <v>132</v>
       </c>
-      <c r="B2" t="s">
-        <v>133</v>
-      </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -895,276 +898,276 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
         <v>47</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>48</v>
-      </c>
-      <c r="D4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
         <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
         <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
         <v>55</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>56</v>
-      </c>
-      <c r="D8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
         <v>59</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>60</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
         <v>63</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
         <v>67</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
         <v>70</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
         <v>73</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
         <v>76</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
         <v>68</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" t="s">
         <v>135</v>
-      </c>
-      <c r="B19" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" t="s">
         <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
         <v>90</v>
-      </c>
-      <c r="D29" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" t="s">
         <v>92</v>
-      </c>
-      <c r="D30" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" t="s">
         <v>94</v>
-      </c>
-      <c r="D31" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1191,10 +1194,10 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -1259,89 +1262,77 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
         <v>40</v>
-      </c>
-      <c r="B2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" t="s">
         <v>38</v>
       </c>
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
       <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -1353,30 +1344,30 @@
         <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
@@ -1388,915 +1379,915 @@
         <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F6" t="s">
         <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F7" t="s">
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H7" t="s">
         <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
       </c>
       <c r="G10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" t="s">
         <v>98</v>
       </c>
-      <c r="H10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" t="s">
-        <v>99</v>
-      </c>
       <c r="K10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
       </c>
       <c r="G11" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" t="s">
         <v>98</v>
       </c>
-      <c r="H11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" t="s">
-        <v>99</v>
-      </c>
       <c r="K11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
         <v>33</v>
       </c>
       <c r="G12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" t="s">
         <v>98</v>
       </c>
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" t="s">
-        <v>99</v>
-      </c>
       <c r="K12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
         <v>33</v>
       </c>
       <c r="G13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J13" t="s">
         <v>98</v>
       </c>
-      <c r="H13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13" t="s">
-        <v>99</v>
-      </c>
       <c r="K13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F14" t="s">
         <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H14" t="s">
         <v>35</v>
       </c>
       <c r="I14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F15" t="s">
         <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
         <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F16" t="s">
         <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H16" t="s">
         <v>35</v>
       </c>
       <c r="I16" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" t="s">
         <v>101</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>102</v>
       </c>
-      <c r="K16" t="s">
-        <v>103</v>
-      </c>
       <c r="L16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F17" t="s">
         <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
         <v>35</v>
       </c>
       <c r="I17" t="s">
+        <v>100</v>
+      </c>
+      <c r="J17" t="s">
         <v>101</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>102</v>
       </c>
-      <c r="K17" t="s">
-        <v>103</v>
-      </c>
       <c r="L17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H18" t="s">
         <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F19" t="s">
         <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H19" t="s">
         <v>35</v>
       </c>
       <c r="I19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F20" t="s">
         <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H20" t="s">
         <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J20" t="s">
+        <v>101</v>
+      </c>
+      <c r="K20" t="s">
         <v>102</v>
       </c>
-      <c r="K20" t="s">
-        <v>103</v>
-      </c>
       <c r="L20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
         <v>33</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H21" t="s">
         <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J21" t="s">
+        <v>101</v>
+      </c>
+      <c r="K21" t="s">
         <v>102</v>
       </c>
-      <c r="K21" t="s">
-        <v>103</v>
-      </c>
       <c r="L21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F22" t="s">
         <v>33</v>
       </c>
       <c r="G22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" t="s">
         <v>98</v>
       </c>
-      <c r="H22" t="s">
-        <v>99</v>
-      </c>
       <c r="I22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F23" t="s">
         <v>33</v>
       </c>
       <c r="G23" t="s">
+        <v>97</v>
+      </c>
+      <c r="H23" t="s">
         <v>98</v>
       </c>
-      <c r="H23" t="s">
-        <v>99</v>
-      </c>
       <c r="I23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24" t="s">
         <v>33</v>
       </c>
       <c r="G24" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" t="s">
         <v>98</v>
       </c>
-      <c r="H24" t="s">
-        <v>99</v>
-      </c>
       <c r="I24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
         <v>33</v>
       </c>
       <c r="G25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" t="s">
         <v>98</v>
       </c>
-      <c r="H25" t="s">
-        <v>99</v>
-      </c>
       <c r="I25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" t="s">
         <v>33</v>
       </c>
       <c r="G26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" t="s">
         <v>98</v>
       </c>
-      <c r="H26" t="s">
-        <v>99</v>
-      </c>
       <c r="I26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
       </c>
       <c r="G27" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" t="s">
         <v>98</v>
       </c>
-      <c r="H27" t="s">
-        <v>99</v>
-      </c>
       <c r="I27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
       </c>
       <c r="G28" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" t="s">
         <v>98</v>
       </c>
-      <c r="H28" t="s">
-        <v>99</v>
-      </c>
       <c r="I28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
         <v>33</v>
       </c>
       <c r="G29" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" t="s">
         <v>98</v>
       </c>
-      <c r="H29" t="s">
-        <v>99</v>
-      </c>
       <c r="I29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s">
         <v>33</v>
       </c>
       <c r="G30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" t="s">
         <v>98</v>
       </c>
-      <c r="H30" t="s">
-        <v>99</v>
-      </c>
       <c r="I30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
       </c>
       <c r="G31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" t="s">
         <v>98</v>
       </c>
-      <c r="H31" t="s">
-        <v>99</v>
-      </c>
       <c r="I31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
       </c>
       <c r="G32" t="s">
+        <v>97</v>
+      </c>
+      <c r="H32" t="s">
         <v>98</v>
       </c>
-      <c r="H32" t="s">
-        <v>99</v>
-      </c>
       <c r="I32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
       </c>
       <c r="G33" t="s">
+        <v>97</v>
+      </c>
+      <c r="H33" t="s">
         <v>98</v>
       </c>
-      <c r="H33" t="s">
-        <v>99</v>
-      </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -2319,24 +2310,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2351,12 +2342,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2375,10 +2366,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" t="s">
         <v>109</v>
-      </c>
-      <c r="B1" t="s">
-        <v>110</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2389,16 +2380,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Downloads/MaHIS dataset reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Documents/Python Scripts/DashPlotly/data/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA81F7E-05B3-574D-86C2-703F2F2659FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF34B275-F339-4045-844A-72ACE042C777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="146">
   <si>
     <t>name</t>
   </si>
@@ -144,9 +144,6 @@
     <t>Encounter</t>
   </si>
   <si>
-    <t>DIAGNOSIS</t>
-  </si>
-  <si>
     <t>concept_name</t>
   </si>
   <si>
@@ -330,9 +327,6 @@
     <t>Over 5</t>
   </si>
   <si>
-    <t>Malaria, presumed</t>
-  </si>
-  <si>
     <t>DISPENSING</t>
   </si>
   <si>
@@ -453,15 +447,6 @@
     <t>MALARIA HEALTH FACILITY MONTHLY REPORT</t>
   </si>
   <si>
-    <t>Yes | Malaria | Malaria</t>
-  </si>
-  <si>
-    <t>Yes | Malaria, presumed | Malaria, presumed</t>
-  </si>
-  <si>
-    <t>Patient pregnant | Primary diagnosis | Secondary diagnosis</t>
-  </si>
-  <si>
     <t>person_id</t>
   </si>
   <si>
@@ -472,6 +457,27 @@
   </si>
   <si>
     <t>Malaria | Positive</t>
+  </si>
+  <si>
+    <t>Malaria</t>
+  </si>
+  <si>
+    <t>Patient pregnant | *diagnosis</t>
+  </si>
+  <si>
+    <t>concept_name | concept_name</t>
+  </si>
+  <si>
+    <t>obs_value_coded | obs_value_coded</t>
+  </si>
+  <si>
+    <t>Yes | Malaria</t>
+  </si>
+  <si>
+    <t>malaria_total_under5</t>
+  </si>
+  <si>
+    <t>malaria_total_over5</t>
   </si>
 </sst>
 </file>
@@ -846,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -881,16 +887,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -898,276 +904,276 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
         <v>46</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>47</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
         <v>49</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
         <v>51</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
         <v>54</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
         <v>66</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>67</v>
-      </c>
-      <c r="D14" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
         <v>69</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
         <v>72</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>73</v>
-      </c>
-      <c r="D16" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
         <v>75</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" t="s">
         <v>67</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="s">
         <v>87</v>
-      </c>
-      <c r="D28" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" t="s">
         <v>89</v>
-      </c>
-      <c r="D29" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" t="s">
         <v>91</v>
-      </c>
-      <c r="D30" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
         <v>93</v>
-      </c>
-      <c r="D31" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{420C8C5D-A000-9B41-8DCF-AB9A394A13A5}">
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
@@ -1194,10 +1200,10 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -1262,695 +1268,659 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
         <v>39</v>
-      </c>
-      <c r="B2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" t="s">
-        <v>38</v>
-      </c>
       <c r="I3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>96</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" t="s">
         <v>140</v>
       </c>
-      <c r="D6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>139</v>
-      </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="I6" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" t="s">
         <v>140</v>
       </c>
-      <c r="D7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" t="s">
-        <v>139</v>
-      </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="I7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>139</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>139</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>98</v>
-      </c>
-      <c r="K10" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
-      </c>
-      <c r="J11" t="s">
-        <v>98</v>
-      </c>
-      <c r="K11" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F12" t="s">
         <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
         <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F14" t="s">
         <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="J14" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F15" t="s">
         <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I15" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="K15" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F16" t="s">
         <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J16" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="K16" t="s">
-        <v>102</v>
-      </c>
-      <c r="L16" t="s">
-        <v>38</v>
-      </c>
-      <c r="M16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F17" t="s">
         <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J17" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="K17" t="s">
-        <v>102</v>
-      </c>
-      <c r="L17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
       </c>
       <c r="G18" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" t="s">
         <v>99</v>
       </c>
-      <c r="H18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" t="s">
-        <v>130</v>
-      </c>
-      <c r="J18" t="s">
-        <v>38</v>
-      </c>
       <c r="K18" t="s">
-        <v>40</v>
+        <v>100</v>
+      </c>
+      <c r="L18" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F19" t="s">
         <v>33</v>
       </c>
       <c r="G19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" t="s">
+        <v>98</v>
+      </c>
+      <c r="J19" t="s">
         <v>99</v>
       </c>
-      <c r="H19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" t="s">
-        <v>130</v>
-      </c>
-      <c r="J19" t="s">
-        <v>38</v>
-      </c>
       <c r="K19" t="s">
-        <v>95</v>
+        <v>100</v>
+      </c>
+      <c r="L19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F20" t="s">
         <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J20" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="K20" t="s">
-        <v>102</v>
-      </c>
-      <c r="L20" t="s">
-        <v>38</v>
-      </c>
-      <c r="M20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F21" t="s">
         <v>33</v>
       </c>
       <c r="G21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J21" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="K21" t="s">
-        <v>102</v>
-      </c>
-      <c r="L21" t="s">
-        <v>38</v>
-      </c>
-      <c r="M21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
         <v>33</v>
@@ -1959,27 +1929,39 @@
         <v>97</v>
       </c>
       <c r="H22" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>128</v>
+      </c>
+      <c r="J22" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" t="s">
+        <v>100</v>
+      </c>
+      <c r="L22" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
         <v>33</v>
@@ -1988,310 +1970,380 @@
         <v>97</v>
       </c>
       <c r="H23" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>104</v>
+        <v>128</v>
+      </c>
+      <c r="J23" t="s">
+        <v>99</v>
+      </c>
+      <c r="K23" t="s">
+        <v>100</v>
+      </c>
+      <c r="L23" t="s">
+        <v>37</v>
+      </c>
+      <c r="M23" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" t="s">
         <v>112</v>
       </c>
-      <c r="C24" t="s">
-        <v>114</v>
-      </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F24" t="s">
         <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s">
         <v>112</v>
       </c>
-      <c r="C25" t="s">
-        <v>114</v>
-      </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
         <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I25" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" t="s">
         <v>112</v>
       </c>
-      <c r="C26" t="s">
-        <v>114</v>
-      </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F26" t="s">
         <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" t="s">
         <v>112</v>
       </c>
-      <c r="C27" t="s">
-        <v>114</v>
-      </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I27" t="s">
-        <v>107</v>
-      </c>
-      <c r="J27" t="s">
-        <v>38</v>
-      </c>
-      <c r="K27" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" t="s">
         <v>112</v>
       </c>
-      <c r="C28" t="s">
-        <v>114</v>
-      </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" t="s">
         <v>112</v>
       </c>
-      <c r="C29" t="s">
-        <v>114</v>
-      </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s">
         <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>105</v>
+      </c>
+      <c r="J29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" t="s">
         <v>112</v>
       </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s">
         <v>33</v>
       </c>
       <c r="G30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" t="s">
         <v>112</v>
       </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
       </c>
       <c r="G31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s">
+        <v>96</v>
+      </c>
+      <c r="I31" t="s">
         <v>98</v>
-      </c>
-      <c r="I31" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
         <v>112</v>
       </c>
-      <c r="C32" t="s">
-        <v>114</v>
-      </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I32" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" t="s">
         <v>112</v>
       </c>
-      <c r="C33" t="s">
-        <v>114</v>
-      </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" t="s">
+        <v>96</v>
+      </c>
+      <c r="I34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J37" s="1"/>
+      <c r="B35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J39" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2310,24 +2362,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2342,12 +2394,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2366,10 +2418,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2380,16 +2432,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Documents/Python Scripts/DashPlotly/data/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF34B275-F339-4045-844A-72ACE042C777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5974DCE-126C-C04F-98AE-4BCB515C2D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33860" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIABLE_NAMES" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="151">
   <si>
     <t>name</t>
   </si>
@@ -369,9 +369,6 @@
     <t>measure</t>
   </si>
   <si>
-    <t>count</t>
-  </si>
-  <si>
     <t>sum</t>
   </si>
   <si>
@@ -426,9 +423,6 @@
     <t>ASAQ 100mg/270mg (3 tablets) | ASAQ 100mg/270mg (6 tablets) | ASAQ 25mg/67.5mg (3 tablets) | ASAQ 50mg/135mg (3 tablets)</t>
   </si>
   <si>
-    <t>Malaria Species | Malaria film</t>
-  </si>
-  <si>
     <t>General</t>
   </si>
   <si>
@@ -453,38 +447,59 @@
     <t>programs</t>
   </si>
   <si>
-    <t>obs_value_coded | Value</t>
-  </si>
-  <si>
-    <t>Malaria | Positive</t>
-  </si>
-  <si>
     <t>Malaria</t>
   </si>
   <si>
-    <t>Patient pregnant | *diagnosis</t>
-  </si>
-  <si>
-    <t>concept_name | concept_name</t>
-  </si>
-  <si>
-    <t>obs_value_coded | obs_value_coded</t>
-  </si>
-  <si>
-    <t>Yes | Malaria</t>
-  </si>
-  <si>
     <t>malaria_total_under5</t>
   </si>
   <si>
     <t>malaria_total_over5</t>
+  </si>
+  <si>
+    <t>nunique</t>
+  </si>
+  <si>
+    <t>concept_name | Value</t>
+  </si>
+  <si>
+    <t>MRDT | Positive</t>
+  </si>
+  <si>
+    <t>concept_name | Value | obs_value_coded</t>
+  </si>
+  <si>
+    <t>MRDT | Positive | Malaria</t>
+  </si>
+  <si>
+    <t>MRDT | !=Positive | Malaria</t>
+  </si>
+  <si>
+    <t>MRDT | !=Positive</t>
+  </si>
+  <si>
+    <t>concept_name | concept_name | Value</t>
+  </si>
+  <si>
+    <t>Patient pregnant | MRDT | !=Positive</t>
+  </si>
+  <si>
+    <t>malaria_tx_failure_under5</t>
+  </si>
+  <si>
+    <t>malaria_tx_failure_over5</t>
+  </si>
+  <si>
+    <t>Malaria Treatment Failure</t>
+  </si>
+  <si>
+    <t>Malaria film</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -494,6 +509,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -519,11 +542,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -852,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -887,10 +911,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
@@ -900,7 +924,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -942,10 +966,10 @@
         <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -964,10 +988,10 @@
         <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1071,18 +1095,18 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
         <v>78</v>
@@ -1090,7 +1114,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -1098,7 +1122,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
         <v>80</v>
@@ -1106,7 +1130,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
         <v>81</v>
@@ -1114,7 +1138,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>82</v>
@@ -1122,7 +1146,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>83</v>
@@ -1130,7 +1154,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>84</v>
@@ -1138,7 +1162,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>85</v>
@@ -1184,15 +1208,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{420C8C5D-A000-9B41-8DCF-AB9A394A13A5}">
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
+    <col min="7" max="7" width="25.1640625" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
@@ -1203,7 +1229,7 @@
         <v>108</v>
       </c>
       <c r="C1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -1271,28 +1297,34 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H2" t="s">
         <v>37</v>
       </c>
       <c r="I2" t="s">
         <v>39</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
@@ -1300,28 +1332,34 @@
         <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
         <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>94</v>
+      </c>
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
@@ -1329,28 +1367,34 @@
         <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H4" t="s">
         <v>37</v>
       </c>
       <c r="I4" t="s">
         <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
@@ -1358,28 +1402,34 @@
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H5" t="s">
         <v>37</v>
       </c>
       <c r="I5" t="s">
         <v>94</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
@@ -1387,28 +1437,34 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" t="s">
         <v>135</v>
-      </c>
-      <c r="D6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G6" t="s">
-        <v>140</v>
-      </c>
-      <c r="H6" t="s">
-        <v>142</v>
-      </c>
-      <c r="I6" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
@@ -1416,51 +1472,57 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
         <v>135</v>
-      </c>
-      <c r="D7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G7" t="s">
-        <v>140</v>
-      </c>
-      <c r="H7" t="s">
-        <v>142</v>
-      </c>
-      <c r="I7" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" t="s">
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
@@ -1471,25 +1533,25 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F9" t="s">
         <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H9" t="s">
         <v>37</v>
@@ -1503,16 +1565,16 @@
         <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
@@ -1526,16 +1588,16 @@
         <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H11" t="s">
         <v>37</v>
@@ -1546,25 +1608,25 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="H12" t="s">
         <v>37</v>
@@ -1572,34 +1634,28 @@
       <c r="I12" t="s">
         <v>39</v>
       </c>
-      <c r="J12" t="s">
-        <v>96</v>
-      </c>
-      <c r="K12" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="H13" t="s">
         <v>37</v>
@@ -1607,110 +1663,116 @@
       <c r="I13" t="s">
         <v>94</v>
       </c>
-      <c r="J13" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F14" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" t="s">
+        <v>142</v>
+      </c>
+      <c r="H14" t="s">
         <v>33</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>95</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>37</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>39</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>96</v>
       </c>
-      <c r="K14" t="s">
-        <v>127</v>
+      <c r="M14" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F15" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H15" t="s">
         <v>33</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>95</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>37</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>94</v>
       </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
         <v>96</v>
       </c>
-      <c r="K15" t="s">
-        <v>127</v>
+      <c r="M15" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F16" t="s">
+        <v>141</v>
+      </c>
+      <c r="G16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" t="s">
         <v>33</v>
       </c>
-      <c r="G16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" t="s">
-        <v>34</v>
-      </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J16" t="s">
         <v>37</v>
@@ -1718,34 +1780,40 @@
       <c r="K16" t="s">
         <v>39</v>
       </c>
+      <c r="L16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M16" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G17" t="s">
+        <v>143</v>
+      </c>
+      <c r="H17" t="s">
         <v>33</v>
       </c>
-      <c r="G17" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" t="s">
-        <v>34</v>
-      </c>
       <c r="I17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J17" t="s">
         <v>37</v>
@@ -1753,22 +1821,28 @@
       <c r="K17" t="s">
         <v>94</v>
       </c>
+      <c r="L17" t="s">
+        <v>96</v>
+      </c>
+      <c r="M17" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
@@ -1783,33 +1857,27 @@
         <v>98</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K18" t="s">
-        <v>100</v>
-      </c>
-      <c r="L18" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F19" t="s">
         <v>33</v>
@@ -1824,33 +1892,27 @@
         <v>98</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K19" t="s">
-        <v>100</v>
-      </c>
-      <c r="L19" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F20" t="s">
         <v>33</v>
@@ -1862,30 +1924,36 @@
         <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="J20" t="s">
+        <v>99</v>
+      </c>
+      <c r="K20" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" t="s">
         <v>37</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F21" t="s">
         <v>33</v>
@@ -1897,30 +1965,36 @@
         <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="J21" t="s">
+        <v>99</v>
+      </c>
+      <c r="K21" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" t="s">
         <v>37</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F22" t="s">
         <v>33</v>
@@ -1932,36 +2006,30 @@
         <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K22" t="s">
-        <v>100</v>
-      </c>
-      <c r="L22" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F23" t="s">
         <v>33</v>
@@ -1973,94 +2041,112 @@
         <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="J23" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K23" t="s">
-        <v>100</v>
-      </c>
-      <c r="L23" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F24" t="s">
         <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H24" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>101</v>
+        <v>150</v>
+      </c>
+      <c r="J24" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" t="s">
+        <v>100</v>
+      </c>
+      <c r="L24" t="s">
+        <v>37</v>
+      </c>
+      <c r="M24" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F25" t="s">
         <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H25" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="I25" t="s">
-        <v>102</v>
+        <v>150</v>
+      </c>
+      <c r="J25" t="s">
+        <v>99</v>
+      </c>
+      <c r="K25" t="s">
+        <v>100</v>
+      </c>
+      <c r="L25" t="s">
+        <v>37</v>
+      </c>
+      <c r="M25" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F26" t="s">
         <v>33</v>
@@ -2072,24 +2158,24 @@
         <v>96</v>
       </c>
       <c r="I26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
@@ -2101,24 +2187,24 @@
         <v>96</v>
       </c>
       <c r="I27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
@@ -2130,24 +2216,24 @@
         <v>96</v>
       </c>
       <c r="I28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s">
         <v>33</v>
@@ -2159,30 +2245,24 @@
         <v>96</v>
       </c>
       <c r="I29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J29" t="s">
-        <v>37</v>
-      </c>
-      <c r="K29" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s">
         <v>33</v>
@@ -2199,19 +2279,19 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
@@ -2223,24 +2303,30 @@
         <v>96</v>
       </c>
       <c r="I31" t="s">
-        <v>98</v>
+        <v>105</v>
+      </c>
+      <c r="J31" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
@@ -2252,24 +2338,24 @@
         <v>96</v>
       </c>
       <c r="I32" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
@@ -2281,24 +2367,24 @@
         <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
@@ -2310,24 +2396,24 @@
         <v>96</v>
       </c>
       <c r="I34" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F35" t="s">
         <v>33</v>
@@ -2339,11 +2425,69 @@
         <v>96</v>
       </c>
       <c r="I35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E36" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" t="s">
+        <v>96</v>
+      </c>
+      <c r="I36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37" t="s">
+        <v>96</v>
+      </c>
+      <c r="I37" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J39" s="1"/>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J41" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2368,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2376,10 +2520,10 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2432,7 +2576,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>

--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Documents/Python Scripts/DashPlotly/data/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A643E14-D666-9D45-A24B-42F541C8D546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B9EB9E-7013-1E44-A595-2A2B1F967CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33860" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="SETTINGS" sheetId="4" r:id="rId4"/>
     <sheet name="DESIGN" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Documents/Python Scripts/DashPlotly/data/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B9EB9E-7013-1E44-A595-2A2B1F967CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3B6F60-ADE2-0046-8B08-0BEC4BAD7D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33860" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="152">
   <si>
     <t>name</t>
   </si>
@@ -493,6 +493,9 @@
   </si>
   <si>
     <t>Malaria film</t>
+  </si>
+  <si>
+    <t>Malaria | Malaria</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1327,7 @@
         <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">

--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Documents/Python Scripts/DashPlotly/data/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3B6F60-ADE2-0046-8B08-0BEC4BAD7D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36D4F1F-2A4A-B347-9B45-D85683F1FAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33860" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33860" windowHeight="19880" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIABLE_NAMES" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="155">
   <si>
     <t>name</t>
   </si>
@@ -327,18 +327,9 @@
     <t>Over 5</t>
   </si>
   <si>
-    <t>DISPENSING</t>
-  </si>
-  <si>
     <t>DrugName</t>
   </si>
   <si>
-    <t>LAB RESULTS</t>
-  </si>
-  <si>
-    <t>MRDT</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -414,15 +405,6 @@
     <t>count_set</t>
   </si>
   <si>
-    <t>Lumefantrine + Arthemether 1 x 6 |Lumefantrine + Arthemether 2 x 6 | Lumefantrine + Arthemether 3 x 6 |Lumefantrine + Arthemether 4 x 6</t>
-  </si>
-  <si>
-    <t>Lumefantrine + Arthemether 1 x 6 |Lumefantrine + Arthemether 2 x 6 | Lumefantrine + Arthemether 3 x 6 |Lumefantrine + Arthemether 4 x 7</t>
-  </si>
-  <si>
-    <t>ASAQ 100mg/270mg (3 tablets) | ASAQ 100mg/270mg (6 tablets) | ASAQ 25mg/67.5mg (3 tablets) | ASAQ 50mg/135mg (3 tablets)</t>
-  </si>
-  <si>
     <t>General</t>
   </si>
   <si>
@@ -447,9 +429,6 @@
     <t>programs</t>
   </si>
   <si>
-    <t>Malaria</t>
-  </si>
-  <si>
     <t>malaria_total_under5</t>
   </si>
   <si>
@@ -462,27 +441,6 @@
     <t>concept_name | Value</t>
   </si>
   <si>
-    <t>MRDT | Positive</t>
-  </si>
-  <si>
-    <t>concept_name | Value | obs_value_coded</t>
-  </si>
-  <si>
-    <t>MRDT | Positive | Malaria</t>
-  </si>
-  <si>
-    <t>MRDT | !=Positive | Malaria</t>
-  </si>
-  <si>
-    <t>MRDT | !=Positive</t>
-  </si>
-  <si>
-    <t>concept_name | concept_name | Value</t>
-  </si>
-  <si>
-    <t>Patient pregnant | MRDT | !=Positive</t>
-  </si>
-  <si>
     <t>malaria_tx_failure_under5</t>
   </si>
   <si>
@@ -495,7 +453,58 @@
     <t>Malaria film</t>
   </si>
   <si>
-    <t>Malaria | Malaria</t>
+    <t>*Malaria</t>
+  </si>
+  <si>
+    <t>Malaria Rapid Diagonostic Test | Positive</t>
+  </si>
+  <si>
+    <t>Dispensing</t>
+  </si>
+  <si>
+    <t>Malaria Rapid Diagonostic Test</t>
+  </si>
+  <si>
+    <t>concept_name | obs_value_coded</t>
+  </si>
+  <si>
+    <t>Patient pregnant | Yes</t>
+  </si>
+  <si>
+    <t>Malaria Rapid Diagonostic Test  | !=Positive</t>
+  </si>
+  <si>
+    <t>*Malaria | Positive</t>
+  </si>
+  <si>
+    <t>Fever</t>
+  </si>
+  <si>
+    <t>total_suspected_malaria_under5</t>
+  </si>
+  <si>
+    <t>total_suspected_malaria_over5</t>
+  </si>
+  <si>
+    <t>*Lumefantrine</t>
+  </si>
+  <si>
+    <t>*ASAQ</t>
+  </si>
+  <si>
+    <t>malaria_presumed_la_under5</t>
+  </si>
+  <si>
+    <t>malaria_presumed_asaq_under5</t>
+  </si>
+  <si>
+    <t>malaria_presumed_asaq_over5</t>
+  </si>
+  <si>
+    <t>malaria_presumed_la_over5</t>
+  </si>
+  <si>
+    <t>!=Malaria Rapid Diagonostic Test</t>
   </si>
 </sst>
 </file>
@@ -879,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -914,10 +923,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
@@ -969,10 +978,10 @@
         <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -991,10 +1000,10 @@
         <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1013,10 +1022,10 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1035,10 +1044,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1090,26 +1099,26 @@
         <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
         <v>78</v>
@@ -1117,7 +1126,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -1125,7 +1134,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
         <v>80</v>
@@ -1133,7 +1142,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>81</v>
@@ -1141,7 +1150,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
         <v>82</v>
@@ -1149,7 +1158,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
         <v>83</v>
@@ -1157,7 +1166,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
         <v>84</v>
@@ -1165,7 +1174,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>85</v>
@@ -1211,14 +1220,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{420C8C5D-A000-9B41-8DCF-AB9A394A13A5}">
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="25.1640625" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" customWidth="1"/>
     <col min="10" max="10" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -1229,10 +1238,10 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -1300,22 +1309,22 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H2" t="s">
         <v>37</v>
@@ -1327,7 +1336,7 @@
         <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
@@ -1335,22 +1344,22 @@
         <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H3" t="s">
         <v>37</v>
@@ -1362,7 +1371,7 @@
         <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
@@ -1370,22 +1379,22 @@
         <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H4" t="s">
         <v>37</v>
@@ -1397,7 +1406,7 @@
         <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
@@ -1405,22 +1414,22 @@
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H5" t="s">
         <v>37</v>
@@ -1432,7 +1441,7 @@
         <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
@@ -1440,34 +1449,40 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="I6" t="s">
+        <v>143</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
         <v>94</v>
       </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
         <v>35</v>
       </c>
-      <c r="K6" t="s">
-        <v>135</v>
+      <c r="M6" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
@@ -1475,57 +1490,63 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="I7" t="s">
+        <v>143</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="s">
         <v>94</v>
       </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>35</v>
       </c>
-      <c r="K7" t="s">
-        <v>135</v>
+      <c r="M7" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F8" t="s">
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
@@ -1536,25 +1557,25 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F9" t="s">
         <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H9" t="s">
         <v>37</v>
@@ -1568,16 +1589,16 @@
         <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
@@ -1591,16 +1612,16 @@
         <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H11" t="s">
         <v>37</v>
@@ -1611,25 +1632,25 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F12" t="s">
         <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="H12" t="s">
         <v>37</v>
@@ -1640,25 +1661,25 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F13" t="s">
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="H13" t="s">
         <v>37</v>
@@ -1672,28 +1693,28 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F14" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="G14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H14" t="s">
         <v>33</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="J14" t="s">
         <v>37</v>
@@ -1702,10 +1723,10 @@
         <v>39</v>
       </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M14" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
@@ -1713,28 +1734,28 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F15" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="G15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H15" t="s">
         <v>33</v>
       </c>
       <c r="I15" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="J15" t="s">
         <v>37</v>
@@ -1743,39 +1764,39 @@
         <v>94</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M15" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F16" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="H16" t="s">
         <v>33</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="J16" t="s">
         <v>37</v>
@@ -1784,39 +1805,39 @@
         <v>39</v>
       </c>
       <c r="L16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M16" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F17" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="H17" t="s">
         <v>33</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="J17" t="s">
         <v>37</v>
@@ -1825,39 +1846,39 @@
         <v>94</v>
       </c>
       <c r="L17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M17" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" t="s">
+        <v>132</v>
+      </c>
+      <c r="G18" t="s">
         <v>138</v>
       </c>
-      <c r="C18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>33</v>
       </c>
-      <c r="G18" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" t="s">
-        <v>34</v>
-      </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="J18" t="s">
         <v>37</v>
@@ -1865,34 +1886,40 @@
       <c r="K18" t="s">
         <v>39</v>
       </c>
+      <c r="L18" t="s">
+        <v>95</v>
+      </c>
+      <c r="M18" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" t="s">
         <v>138</v>
       </c>
-      <c r="C19" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" t="s">
-        <v>121</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>33</v>
       </c>
-      <c r="G19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" t="s">
-        <v>34</v>
-      </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="J19" t="s">
         <v>37</v>
@@ -1900,116 +1927,122 @@
       <c r="K19" t="s">
         <v>94</v>
       </c>
+      <c r="L19" t="s">
+        <v>95</v>
+      </c>
+      <c r="M19" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" t="s">
         <v>33</v>
       </c>
-      <c r="G20" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" t="s">
-        <v>34</v>
-      </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="J20" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K20" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="L20" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="M20" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21" t="s">
         <v>33</v>
       </c>
-      <c r="G21" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" t="s">
-        <v>34</v>
-      </c>
       <c r="I21" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="J21" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K21" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L21" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="M21" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="H22" t="s">
         <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J22" t="s">
         <v>37</v>
@@ -2020,31 +2053,31 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="H23" t="s">
         <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J23" t="s">
         <v>37</v>
@@ -2055,442 +2088,640 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" t="s">
         <v>97</v>
       </c>
-      <c r="H24" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" t="s">
-        <v>150</v>
-      </c>
       <c r="J24" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K24" t="s">
-        <v>100</v>
-      </c>
-      <c r="L24" t="s">
-        <v>37</v>
-      </c>
-      <c r="M24" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25" t="s">
         <v>97</v>
       </c>
-      <c r="H25" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" t="s">
-        <v>150</v>
-      </c>
       <c r="J25" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="K25" t="s">
-        <v>100</v>
-      </c>
-      <c r="L25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M25" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="H26" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>101</v>
+        <v>136</v>
+      </c>
+      <c r="J26" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G27" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="H27" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="I27" t="s">
-        <v>102</v>
+        <v>136</v>
+      </c>
+      <c r="J27" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="H28" t="s">
         <v>96</v>
       </c>
       <c r="I28" t="s">
-        <v>103</v>
+        <v>97</v>
+      </c>
+      <c r="J28" t="s">
+        <v>37</v>
+      </c>
+      <c r="K28" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G29" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="H29" t="s">
         <v>96</v>
       </c>
       <c r="I29" t="s">
-        <v>104</v>
+        <v>97</v>
+      </c>
+      <c r="J29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G30" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="H30" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="I30" t="s">
-        <v>105</v>
+        <v>137</v>
+      </c>
+      <c r="J30" t="s">
+        <v>37</v>
+      </c>
+      <c r="K30" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G31" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="H31" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="J31" t="s">
         <v>37</v>
       </c>
       <c r="K31" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
       </c>
       <c r="G32" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" t="s">
         <v>95</v>
       </c>
-      <c r="H32" t="s">
-        <v>96</v>
-      </c>
       <c r="I32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
       </c>
       <c r="G33" t="s">
+        <v>139</v>
+      </c>
+      <c r="H33" t="s">
         <v>95</v>
       </c>
-      <c r="H33" t="s">
-        <v>96</v>
-      </c>
       <c r="I33" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
       </c>
       <c r="G34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H34" t="s">
         <v>95</v>
       </c>
-      <c r="H34" t="s">
-        <v>96</v>
-      </c>
       <c r="I34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E35" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F35" t="s">
         <v>33</v>
       </c>
       <c r="G35" t="s">
+        <v>139</v>
+      </c>
+      <c r="H35" t="s">
         <v>95</v>
       </c>
-      <c r="H35" t="s">
-        <v>96</v>
-      </c>
       <c r="I35" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F36" t="s">
         <v>33</v>
       </c>
       <c r="G36" t="s">
+        <v>139</v>
+      </c>
+      <c r="H36" t="s">
         <v>95</v>
       </c>
-      <c r="H36" t="s">
-        <v>96</v>
-      </c>
       <c r="I36" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F37" t="s">
         <v>33</v>
       </c>
       <c r="G37" t="s">
+        <v>139</v>
+      </c>
+      <c r="H37" t="s">
         <v>95</v>
       </c>
-      <c r="H37" t="s">
-        <v>96</v>
-      </c>
       <c r="I37" t="s">
+        <v>102</v>
+      </c>
+      <c r="J37" t="s">
+        <v>37</v>
+      </c>
+      <c r="K37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" t="s">
+        <v>118</v>
+      </c>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
+        <v>139</v>
+      </c>
+      <c r="H38" t="s">
+        <v>95</v>
+      </c>
+      <c r="I38" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" t="s">
+        <v>118</v>
+      </c>
+      <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
+        <v>139</v>
+      </c>
+      <c r="H39" t="s">
+        <v>95</v>
+      </c>
+      <c r="I39" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
+        <v>139</v>
+      </c>
+      <c r="H40" t="s">
+        <v>95</v>
+      </c>
+      <c r="I40" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41" t="s">
+        <v>95</v>
+      </c>
+      <c r="I41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" t="s">
+        <v>119</v>
+      </c>
+      <c r="E42" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>139</v>
+      </c>
+      <c r="H42" t="s">
+        <v>95</v>
+      </c>
+      <c r="I42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>139</v>
+      </c>
+      <c r="H43" t="s">
+        <v>95</v>
+      </c>
+      <c r="I43" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J41" s="1"/>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J47" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2515,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2523,10 +2754,10 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2565,10 +2796,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2579,7 +2810,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>

--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Documents/Python Scripts/DashPlotly/data/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36D4F1F-2A4A-B347-9B45-D85683F1FAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0C07D4-5927-314A-BFE5-718F16F4792D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33860" windowHeight="19880" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33860" windowHeight="19880" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIABLE_NAMES" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="253">
   <si>
     <t>name</t>
   </si>
@@ -168,9 +168,6 @@
     <t>malaria_report</t>
   </si>
   <si>
-    <t>Malaria Report</t>
-  </si>
-  <si>
     <t>period</t>
   </si>
   <si>
@@ -351,12 +348,6 @@
     <t>Insecticide treated net</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Sub_Title</t>
-  </si>
-  <si>
     <t>measure</t>
   </si>
   <si>
@@ -369,9 +360,6 @@
     <t>ValueN</t>
   </si>
   <si>
-    <t>Monthly Health Facility Malaria Report</t>
-  </si>
-  <si>
     <t>LA 1X6</t>
   </si>
   <si>
@@ -477,9 +465,6 @@
     <t>*Malaria | Positive</t>
   </si>
   <si>
-    <t>Fever</t>
-  </si>
-  <si>
     <t>total_suspected_malaria_under5</t>
   </si>
   <si>
@@ -504,14 +489,1775 @@
     <t>malaria_presumed_la_over5</t>
   </si>
   <si>
-    <t>!=Malaria Rapid Diagonostic Test</t>
+    <t>calculated</t>
+  </si>
+  <si>
+    <t>FILTERS Sheet — Filling Guide</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Each row in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FILTERS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sheet defines one named filter whose computed value can be placed anywhere in the report via the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VARIABLE_NAMES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sheet.</t>
+    </r>
+  </si>
+  <si>
+    <t>Column reference</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <t>Unique identifier for this filter. Referenced by the VARIABLE_NAMES sheet. No spaces recommended (use underscores).</t>
+  </si>
+  <si>
+    <t>What computation to perform. See measure types below.</t>
+  </si>
+  <si>
+    <t>✅*</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The column used to group/aggregate (e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>patient_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">). For </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>calculated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> measure, put the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>expression</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> here instead.</t>
+    </r>
+  </si>
+  <si>
+    <t>num_field</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Numeric column to sum (only used by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>cohort_sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>). Defaults to the system numeric field if blank.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>variable1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> … </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>variable9</t>
+    </r>
+  </si>
+  <si>
+    <t>Data columns to filter on. Add pairs left-to-right; stop when no more conditions are needed.</t>
+  </si>
+  <si>
+    <r>
+      <t>value1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> … </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>value9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Accepted value(s) for the matching </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>variableN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> column.</t>
+    </r>
+  </si>
+  <si>
+    <t>literal_value</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Only for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>literal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> measure. The exact text/number to display.</t>
+    </r>
+  </si>
+  <si>
+    <t>numerator_filter</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Only for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>percentage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> measure. The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>filter_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the numerator row.</t>
+    </r>
+  </si>
+  <si>
+    <t>denominator_filter</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Only for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>percentage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> measure. The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>filter_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the denominator row.</t>
+    </r>
+  </si>
+  <si>
+    <t>Measure types</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Counts rows in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>filtered</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dataset matching all variable/value pairs.</t>
+    </r>
+  </si>
+  <si>
+    <t>new_clients</t>
+  </si>
+  <si>
+    <t>patient_id</t>
+  </si>
+  <si>
+    <t>enrollment_type</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Same behaviour as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (counts distinct unique_column entries). Use when you want to be explicit that you are counting unique individuals.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Counts using set logic (each unique_column counted once per matching set of conditions). Uses the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>filtered</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dataset.</t>
+    </r>
+  </si>
+  <si>
+    <t>cohort_count</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Like </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> but runs against the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>original (unfiltered)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dataset. Use for cohort denominators that must not be restricted by the active date/site filter.</t>
+    </r>
+  </si>
+  <si>
+    <t>cohort_count_set</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Like </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>count_set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> but against the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>original</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dataset.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>count_defaulter</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>cohort_count_defaulter</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>cohort_count_set_defaulter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Defaulter variants. Behave like their base measure but automatically include the appointment/defaulter-related columns (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>concept_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>value_datetime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) in the query. Use for missed-appointment or IIT indicators.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sums the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>num_field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> column for matching rows. Uses the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>filtered</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dataset.</t>
+    </r>
+  </si>
+  <si>
+    <t>total_cd4</t>
+  </si>
+  <si>
+    <t>cd4_value</t>
+  </si>
+  <si>
+    <t>test_type</t>
+  </si>
+  <si>
+    <t>CD4</t>
+  </si>
+  <si>
+    <t>cohort_sum</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Like </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> but against the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>original</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dataset.</t>
+    </r>
+  </si>
+  <si>
+    <t>percentage</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Divides one filter's result by another and multiplies by 100. Result is displayed as e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>87.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Leave all </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>variableN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>valueN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> columns blank. Fill only:</t>
+    </r>
+  </si>
+  <si>
+    <t>vl_suppression_rate</t>
+  </si>
+  <si>
+    <t>vl_suppressed</t>
+  </si>
+  <si>
+    <t>vl_tested</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Both </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>numerator_filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>denominator_filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must be </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>filter_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> values defined elsewhere in the sheet.</t>
+    </r>
+  </si>
+  <si>
+    <t>literal</t>
+  </si>
+  <si>
+    <t>Outputs a fixed text or number exactly as written. Useful for static labels or target values.</t>
+  </si>
+  <si>
+    <t>target_label</t>
+  </si>
+  <si>
+    <t>Leave all other columns blank.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Evaluates an arithmetic expression referencing other filters by name. The expression goes in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>unique_column</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> column (not </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>literal_value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write filter names wrapped in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>{}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Standard operators </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are supported.</t>
+    </r>
+  </si>
+  <si>
+    <t>net_new</t>
+  </si>
+  <si>
+    <t>{enrolled} - {transferred_out}</t>
+  </si>
+  <si>
+    <t>ratio_per_100</t>
+  </si>
+  <si>
+    <t>{positive} / {tested} * 100</t>
+  </si>
+  <si>
+    <t>Formatting rules applied automatically:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Expression contains </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → result rounded to max 2 decimal places (trailing zeros removed, e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>3.50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>3.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → result is a whole integer, no decimal places</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">All filters referenced in the expression are computed before any </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>calculated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> filter is evaluated, so the referenced filters may be defined in any order and can belong to different report sections.</t>
+    </r>
+  </si>
+  <si>
+    <t>Filtering values — syntax</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A single </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>valueN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cell can hold one value, a list, or a pipe-separated set:</t>
+    </r>
+  </si>
+  <si>
+    <t>Syntax</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Match exactly </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Positive</t>
+    </r>
+  </si>
+  <si>
+    <t>Positive|Reactive</t>
+  </si>
+  <si>
+    <t>Match either value (OR logic)</t>
+  </si>
+  <si>
+    <t>[Positive, Reactive]</t>
+  </si>
+  <si>
+    <t>Same — bracket list syntax</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A blank </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>valueN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> means no filtering on that variable (all values accepted).</t>
+    </r>
+  </si>
+  <si>
+    <t>Quick rules</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Every row must have a unique </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>filter_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Duplicate names silently overwrite each other.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>variable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pairs are read left-to-right and stop at the first blank </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>variableN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Do not leave gaps in the middle.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>calculated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, leave </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>num_field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>literal_value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>numerator_filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>denominator_filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and all </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>variable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> columns blank.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>percentage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, leave </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>unique_column</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>num_field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>literal_value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and all </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>variable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> columns blank.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>literal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>filter_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>measure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>literal_value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are needed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cohort_*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> measures query the full original dataset regardless of the active report date range or site filter. All other measures query the pre-filtered dataset.</t>
+    </r>
+  </si>
+  <si>
+    <t>female_pregnant_with_malaria</t>
+  </si>
+  <si>
+    <t>CALCULATED FIELDS</t>
+  </si>
+  <si>
+    <t>female_pregnant_tested_positive_for_malaria</t>
+  </si>
+  <si>
+    <t>{female_pregnant_with_malaria}-{female_pregnant_tested_positive_for_malaria}</t>
+  </si>
+  <si>
+    <t>total_malaria_cases_u5</t>
+  </si>
+  <si>
+    <t>total_malaria_cases_o5</t>
+  </si>
+  <si>
+    <t>{total_malaria_cases_u5}-{malaria_confirmed_under5}</t>
+  </si>
+  <si>
+    <t>{total_malaria_cases_o5}-{malaria_confirmed_over5}</t>
+  </si>
+  <si>
+    <t>{malaria_confirmed_under5}+{malaria_presumed_under5}</t>
+  </si>
+  <si>
+    <t>{malaria_confirmed_over5}+{malaria_presumed_over5}+{malaria_pregnant_over5}+{malaria_pregnant_presumed_over5}</t>
+  </si>
+  <si>
+    <t>all_cases_receiveing_LA_o5</t>
+  </si>
+  <si>
+    <t>all_cases_receiveing_LA_u5</t>
+  </si>
+  <si>
+    <t>all_cases_receiveing_ASAQ_u5</t>
+  </si>
+  <si>
+    <t>all_cases_receiveing_ASAQ_o5</t>
+  </si>
+  <si>
+    <t>{all_cases_receiveing_LA_u5}-{confirmed_la_under5}</t>
+  </si>
+  <si>
+    <t>{all_cases_receiveing_LA_o5}-{confirmed_la_over5}</t>
+  </si>
+  <si>
+    <t>{all_cases_receiveing_ASAQ_u5}-{confirmed_asaq_under5}</t>
+  </si>
+  <si>
+    <t>{all_cases_receiveing_ASAQ_o5}-{confirmed_asaq_over5}</t>
+  </si>
+  <si>
+    <t>*Fever</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -529,6 +2275,50 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -554,17 +2344,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -888,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -923,16 +2729,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -948,268 +2754,268 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>46</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
         <v>48</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
         <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>54</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>58</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
         <v>61</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
         <v>65</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>66</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
         <v>68</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
         <v>71</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
         <v>74</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" t="s">
         <v>86</v>
-      </c>
-      <c r="D28" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" t="s">
         <v>88</v>
-      </c>
-      <c r="D29" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" t="s">
         <v>90</v>
-      </c>
-      <c r="D30" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" t="s">
         <v>92</v>
-      </c>
-      <c r="D31" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1220,7 +3026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{420C8C5D-A000-9B41-8DCF-AB9A394A13A5}">
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
@@ -1238,10 +3044,10 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -1309,22 +3115,22 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H2" t="s">
         <v>37</v>
@@ -1336,7 +3142,7 @@
         <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
@@ -1344,261 +3150,147 @@
         <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
         <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J3" t="s">
         <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" t="s">
-        <v>137</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>154</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>94</v>
-      </c>
-      <c r="J5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="J6" t="s">
         <v>37</v>
       </c>
       <c r="K6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L6" t="s">
         <v>35</v>
       </c>
       <c r="M6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" t="s">
-        <v>132</v>
-      </c>
-      <c r="I7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" t="s">
-        <v>137</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>137</v>
-      </c>
-      <c r="H8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" t="s">
-        <v>39</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>137</v>
-      </c>
-      <c r="H9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" t="s">
-        <v>94</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
@@ -1609,48 +3301,48 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H11" t="s">
         <v>37</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F12" t="s">
         <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H12" t="s">
         <v>37</v>
@@ -1661,60 +3353,60 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F13" t="s">
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H13" t="s">
         <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
         <v>33</v>
       </c>
       <c r="I14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J14" t="s">
         <v>37</v>
@@ -1723,162 +3415,102 @@
         <v>39</v>
       </c>
       <c r="L14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M14" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G15" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H15" t="s">
         <v>33</v>
       </c>
       <c r="I15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J15" t="s">
         <v>37</v>
       </c>
       <c r="K15" t="s">
+        <v>93</v>
+      </c>
+      <c r="L15" t="s">
         <v>94</v>
       </c>
-      <c r="L15" t="s">
-        <v>95</v>
-      </c>
       <c r="M15" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J16" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" t="s">
-        <v>39</v>
-      </c>
-      <c r="L16" t="s">
-        <v>95</v>
-      </c>
-      <c r="M16" t="s">
-        <v>148</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" t="s">
-        <v>154</v>
-      </c>
-      <c r="H17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" t="s">
-        <v>139</v>
-      </c>
-      <c r="J17" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" t="s">
-        <v>94</v>
-      </c>
-      <c r="L17" t="s">
-        <v>95</v>
-      </c>
-      <c r="M17" t="s">
-        <v>148</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F18" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G18" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H18" t="s">
         <v>33</v>
       </c>
       <c r="I18" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J18" t="s">
         <v>37</v>
@@ -1887,162 +3519,102 @@
         <v>39</v>
       </c>
       <c r="L18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M18" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G19" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H19" t="s">
         <v>33</v>
       </c>
       <c r="I19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J19" t="s">
         <v>37</v>
       </c>
       <c r="K19" t="s">
+        <v>93</v>
+      </c>
+      <c r="L19" t="s">
         <v>94</v>
       </c>
-      <c r="L19" t="s">
-        <v>95</v>
-      </c>
       <c r="M19" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" t="s">
-        <v>154</v>
-      </c>
-      <c r="H20" t="s">
-        <v>33</v>
-      </c>
-      <c r="I20" t="s">
-        <v>139</v>
-      </c>
-      <c r="J20" t="s">
-        <v>37</v>
-      </c>
-      <c r="K20" t="s">
-        <v>39</v>
-      </c>
-      <c r="L20" t="s">
-        <v>95</v>
-      </c>
-      <c r="M20" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" t="s">
-        <v>154</v>
-      </c>
-      <c r="H21" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" t="s">
-        <v>139</v>
-      </c>
-      <c r="J21" t="s">
-        <v>37</v>
-      </c>
-      <c r="K21" t="s">
-        <v>94</v>
-      </c>
-      <c r="L21" t="s">
-        <v>95</v>
-      </c>
-      <c r="M21" t="s">
-        <v>149</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="H22" t="s">
         <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J22" t="s">
         <v>37</v>
@@ -2053,66 +3625,66 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="H23" t="s">
         <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J23" t="s">
         <v>37</v>
       </c>
       <c r="K23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
       </c>
       <c r="G24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H24" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" t="s">
         <v>96</v>
-      </c>
-      <c r="I24" t="s">
-        <v>97</v>
       </c>
       <c r="J24" t="s">
         <v>37</v>
@@ -2123,66 +3695,66 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
       </c>
       <c r="G25" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H25" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" t="s">
         <v>96</v>
-      </c>
-      <c r="I25" t="s">
-        <v>97</v>
       </c>
       <c r="J25" t="s">
         <v>37</v>
       </c>
       <c r="K25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F26" t="s">
         <v>34</v>
       </c>
       <c r="G26" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="H26" t="s">
         <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J26" t="s">
         <v>37</v>
@@ -2193,66 +3765,66 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
       </c>
       <c r="G27" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="H27" t="s">
         <v>34</v>
       </c>
       <c r="I27" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J27" t="s">
         <v>37</v>
       </c>
       <c r="K27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H28" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" t="s">
         <v>96</v>
-      </c>
-      <c r="I28" t="s">
-        <v>97</v>
       </c>
       <c r="J28" t="s">
         <v>37</v>
@@ -2263,66 +3835,66 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H29" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" t="s">
         <v>96</v>
-      </c>
-      <c r="I29" t="s">
-        <v>97</v>
       </c>
       <c r="J29" t="s">
         <v>37</v>
       </c>
       <c r="K29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
       </c>
       <c r="G30" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="H30" t="s">
         <v>34</v>
       </c>
       <c r="I30" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J30" t="s">
         <v>37</v>
@@ -2333,211 +3905,211 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="H31" t="s">
         <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J31" t="s">
         <v>37</v>
       </c>
       <c r="K31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
       </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F35" t="s">
         <v>33</v>
       </c>
       <c r="G35" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E36" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F36" t="s">
         <v>33</v>
       </c>
       <c r="G36" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F37" t="s">
         <v>33</v>
       </c>
       <c r="G37" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J37" t="s">
         <v>37</v>
@@ -2546,185 +4118,481 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F38" t="s">
         <v>33</v>
       </c>
       <c r="G38" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
         <v>33</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F40" t="s">
         <v>33</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F41" t="s">
         <v>33</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F42" t="s">
         <v>33</v>
       </c>
       <c r="G42" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F43" t="s">
         <v>33</v>
       </c>
       <c r="G43" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="J47" s="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>234</v>
+      </c>
+      <c r="B46" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" t="s">
+        <v>114</v>
+      </c>
+      <c r="F46" t="s">
+        <v>137</v>
+      </c>
+      <c r="G46" t="s">
+        <v>138</v>
+      </c>
+      <c r="H46" t="s">
+        <v>37</v>
+      </c>
+      <c r="I46" t="s">
+        <v>93</v>
+      </c>
+      <c r="J46" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>236</v>
+      </c>
+      <c r="B47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" t="s">
+        <v>137</v>
+      </c>
+      <c r="G47" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="J47" t="s">
+        <v>37</v>
+      </c>
+      <c r="K47" t="s">
+        <v>93</v>
+      </c>
+      <c r="L47" t="s">
+        <v>35</v>
+      </c>
+      <c r="M47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J48" s="1"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" t="s">
+        <v>123</v>
+      </c>
+      <c r="D50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" t="s">
+        <v>133</v>
+      </c>
+      <c r="H50" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>239</v>
+      </c>
+      <c r="B51" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" t="s">
+        <v>115</v>
+      </c>
+      <c r="E51" t="s">
+        <v>114</v>
+      </c>
+      <c r="F51" t="s">
+        <v>35</v>
+      </c>
+      <c r="G51" t="s">
+        <v>133</v>
+      </c>
+      <c r="H51" t="s">
+        <v>37</v>
+      </c>
+      <c r="I51" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>245</v>
+      </c>
+      <c r="B53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" t="s">
+        <v>115</v>
+      </c>
+      <c r="E53" t="s">
+        <v>114</v>
+      </c>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53" t="s">
+        <v>135</v>
+      </c>
+      <c r="H53" t="s">
+        <v>37</v>
+      </c>
+      <c r="I53" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" t="s">
+        <v>94</v>
+      </c>
+      <c r="K53" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>244</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" t="s">
+        <v>123</v>
+      </c>
+      <c r="D54" t="s">
+        <v>115</v>
+      </c>
+      <c r="E54" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" t="s">
+        <v>135</v>
+      </c>
+      <c r="H54" t="s">
+        <v>37</v>
+      </c>
+      <c r="I54" t="s">
+        <v>93</v>
+      </c>
+      <c r="J54" t="s">
+        <v>94</v>
+      </c>
+      <c r="K54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>246</v>
+      </c>
+      <c r="B56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" t="s">
+        <v>123</v>
+      </c>
+      <c r="D56" t="s">
+        <v>115</v>
+      </c>
+      <c r="E56" t="s">
+        <v>114</v>
+      </c>
+      <c r="F56" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" t="s">
+        <v>135</v>
+      </c>
+      <c r="H56" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" t="s">
+        <v>39</v>
+      </c>
+      <c r="J56" t="s">
+        <v>94</v>
+      </c>
+      <c r="K56" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>247</v>
+      </c>
+      <c r="B57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" t="s">
+        <v>135</v>
+      </c>
+      <c r="H57" t="s">
+        <v>37</v>
+      </c>
+      <c r="I57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J57" t="s">
+        <v>94</v>
+      </c>
+      <c r="K57" t="s">
+        <v>144</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B7 B10:B54 B56:B1048576">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B54 B56:B1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="calculated">
+      <formula>NOT(ISERROR(SEARCH("calculated",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -2746,7 +4614,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2754,10 +4622,10 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2772,12 +4640,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2787,39 +4655,536 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C148B2C-C1CD-AC49-BD11-14CF93C0673F}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="31" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="24" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="63" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>94</v>
+      <c r="D65" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>190</v>
+      </c>
+      <c r="B66" t="s">
+        <v>103</v>
+      </c>
+      <c r="C66" t="s">
+        <v>178</v>
+      </c>
+      <c r="D66" t="s">
+        <v>191</v>
+      </c>
+      <c r="E66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F66" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A75" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>199</v>
+      </c>
+      <c r="B82" t="s">
+        <v>196</v>
+      </c>
+      <c r="C82" t="s">
+        <v>200</v>
+      </c>
+      <c r="D82" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>205</v>
+      </c>
+      <c r="B93" t="s">
+        <v>203</v>
+      </c>
+      <c r="C93">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A99" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>209</v>
+      </c>
+      <c r="B106" t="s">
+        <v>149</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>211</v>
+      </c>
+      <c r="B107" t="s">
+        <v>149</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="17" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="24" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B123" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+      <c r="A124" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B124" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B125" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A138" s="5" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
